--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/WEST_VIRGINIA_2021.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/WEST_VIRGINIA_2021.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -457,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Pantelhó</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -573,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -589,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -602,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -628,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -672,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -687,12 +757,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C23">
@@ -703,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>San Antonio la Isla</t>
+          <t>San Antonio La Isla</t>
         </is>
       </c>
       <c r="C24">
@@ -716,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C25">
@@ -729,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -742,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -762,7 +852,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C28">
@@ -773,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -786,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C30">
@@ -799,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -812,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Total</t>
@@ -843,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C34">
@@ -856,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C35">
@@ -869,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C36">
@@ -882,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -895,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C38">
@@ -908,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Total</t>
@@ -939,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -952,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -978,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mineral del Chico</t>
+          <t>Mineral Del Chico</t>
         </is>
       </c>
       <c r="C44">
@@ -991,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C45">
@@ -1004,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C46">
@@ -1017,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1037,7 +1212,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Atotonilco el Alto</t>
+          <t>Atotonilco El Alto</t>
         </is>
       </c>
       <c r="C48">
@@ -1048,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1061,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C50">
@@ -1074,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1087,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -1100,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -1113,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1126,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1157,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -1170,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -1183,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Purépero</t>
@@ -1196,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1227,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -1240,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1271,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1302,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>San Lucas Ojitlán</t>
@@ -1315,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>San Pedro Pochutla</t>
@@ -1328,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Santa María Huatulco</t>
@@ -1341,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Santa María Zacatepec</t>
@@ -1354,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -1367,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Santiago Yaitepec</t>
@@ -1380,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C73">
@@ -1393,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Unión Hidalgo</t>
@@ -1406,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1437,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Honey</t>
@@ -1450,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Jalpan</t>
@@ -1463,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -1476,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Tlacuilotepec</t>
@@ -1489,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1509,7 +1824,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C82">
@@ -1520,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1533,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1564,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Matehuala</t>
@@ -1577,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -1590,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1621,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1652,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1683,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -1696,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Calcahualco</t>
@@ -1709,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -1722,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -1735,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -1748,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -1761,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C100">
@@ -1774,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -1787,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -1800,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -1813,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Tlachichilco</t>
@@ -1826,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -1839,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1870,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -1883,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1906,41 +2331,6 @@
       </c>
       <c r="D110">
         <v>1</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 701,861</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Mayo de 2022</t>
-        </is>
       </c>
     </row>
   </sheetData>
